--- a/data/macro/FED Target Rate.xlsx
+++ b/data/macro/FED Target Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4934FEA-6A3F-400F-84D2-662FA5D93112}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDD993F-FDC1-F64F-8EDD-4C1F8514E7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10160" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
@@ -55,27 +55,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -83,14 +83,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -121,15 +121,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -408,15 +408,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E295"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="9" style="3"/>
     <col min="6" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>30221</v>
       </c>
@@ -444,7 +444,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>30225</v>
       </c>
@@ -458,7 +458,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>30231</v>
       </c>
@@ -472,7 +472,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>30274</v>
       </c>
@@ -486,7 +486,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>30299</v>
       </c>
@@ -500,7 +500,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>30406</v>
       </c>
@@ -514,7 +514,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>30461</v>
       </c>
@@ -528,7 +528,7 @@
         <v>8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>30491</v>
       </c>
@@ -542,7 +542,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>30511</v>
       </c>
@@ -556,7 +556,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>30517</v>
       </c>
@@ -570,7 +570,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>30539</v>
       </c>
@@ -584,7 +584,7 @@
         <v>9.4299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>30545</v>
       </c>
@@ -598,7 +598,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>30574</v>
       </c>
@@ -612,7 +612,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>30770</v>
       </c>
@@ -626,7 +626,7 @@
         <v>9.3700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>30868</v>
       </c>
@@ -640,7 +640,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>30882</v>
       </c>
@@ -654,7 +654,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>30903</v>
       </c>
@@ -668,7 +668,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>30945</v>
       </c>
@@ -682,7 +682,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>30952</v>
       </c>
@@ -696,7 +696,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>30966</v>
       </c>
@@ -710,7 +710,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>30973</v>
       </c>
@@ -724,7 +724,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>30994</v>
       </c>
@@ -738,7 +738,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>31009</v>
       </c>
@@ -752,7 +752,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>31022</v>
       </c>
@@ -766,7 +766,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>31035</v>
       </c>
@@ -780,7 +780,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>31040</v>
       </c>
@@ -794,7 +794,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>31071</v>
       </c>
@@ -808,7 +808,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>31092</v>
       </c>
@@ -822,7 +822,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>31134</v>
       </c>
@@ -836,7 +836,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>31162</v>
       </c>
@@ -850,7 +850,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31187</v>
       </c>
@@ -864,7 +864,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31239</v>
       </c>
@@ -878,7 +878,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>31253</v>
       </c>
@@ -892,7 +892,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31280</v>
       </c>
@@ -906,7 +906,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>31296</v>
       </c>
@@ -920,7 +920,7 @@
         <v>7.8100000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>31399</v>
       </c>
@@ -934,7 +934,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>31478</v>
       </c>
@@ -948,7 +948,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>31504</v>
       </c>
@@ -962,7 +962,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>31523</v>
       </c>
@@ -976,7 +976,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>31554</v>
       </c>
@@ -990,7 +990,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>31568</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>31604</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>31645</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>6.3700000000000007E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>31782</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>31897</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>31919</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>31960</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>32016</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>32023</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>32024</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>32044</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>32085</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>32170</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>32184</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>32232</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>32272</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>32288</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>32316</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>32325</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>7.4300000000000005E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>32343</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>32363</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>32364</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>32464</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>32469</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>32492</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>32513</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>32548</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>32553</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>32563</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>32645</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>32665</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>9.8100000000000007E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>32696</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>32716</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>32800</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>32818</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>32862</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>33067</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>33175</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>33191</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>33214</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>33226</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>33247</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>33270</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>33305</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>33358</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>33456</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>33494</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>33542</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>33548</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>33578</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>33592</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>33703</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>33787</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>33851</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>34369</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>34415</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>34442</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>34471</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>34562</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>34653</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>34731</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>34886</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>35052</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>35095</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>35514</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>36067</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>36083</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>36116</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>36341</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>36396</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>36480</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>36558</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>36606</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>36662</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>36894</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>36922</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>36970</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>36999</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>37026</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>37069</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>37124</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>37151</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>37166</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>37201</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>37236</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>37566</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>37797</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>38168</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>38209</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>38251</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>38301</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>38335</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>38385</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>38433</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>38475</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>38533</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>38573</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>38615</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>38657</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>38699</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>38748</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>38804</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>38847</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38897</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39343</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>39386</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>39427</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>39469</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>39477</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>39525</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>39568</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>39624</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>39665</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>39707</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>39729</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>39750</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>39798</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>39841</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>39890</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>39932</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>39988</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>40037</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>40079</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>40121</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>40163</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>40205</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>40253</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>40296</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>40352</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>40400</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>40442</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>40485</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>40526</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>40569</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>40617</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>40660</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>40716</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>40764</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>40807</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>40849</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>40890</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>40933</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>40981</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>41024</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>41080</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>41122</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>41165</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>41206</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>41255</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>41304</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>41353</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>41395</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>41444</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>41486</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>41535</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>41577</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>41626</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>41668</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>41717</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>41759</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>41808</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>41850</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>41899</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>41941</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>41990</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>42032</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>42081</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>42123</v>
       </c>
@@ -3513,7 +3513,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>42172</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>42214</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>42264</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>42305</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>42354</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>42396</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>42445</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>42487</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>42536</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>42578</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>42634</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>42676</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>42718</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>42767</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>42809</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>42858</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>42900</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>42942</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>42998</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>43040</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>43082</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>43131</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>43180</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>43222</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>43264</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>43313</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>43369</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>43412</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>43453</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>43495</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>43544</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>43586</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>43635</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>43677</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>43726</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>43768</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>43810</v>
       </c>
@@ -4142,7 +4142,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>43859</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>43893</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>43905</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>43950</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>43992</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>44041</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>44090</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>44140</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44181</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>44223</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>44272</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>44314</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>44363</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>44405</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>44461</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>44503</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>44545</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>44587</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>44636</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>44685</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>44727</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>44769</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>44825</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>44867</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>44909</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>44958</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>45007</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>45049</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>45091</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>45133</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>45189</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>45231</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>45273</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>45322</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45371</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45413</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45455</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45504</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45553</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45603</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45644</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45686</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45735</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45784</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45826</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45868</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45917</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45959</v>
       </c>
@@ -4952,12 +4952,12 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>46001</v>
       </c>
       <c r="B295" s="2">
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="C295" s="3">
         <v>3.7499999999999999E-2</v>
@@ -4978,12 +4978,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
